--- a/r5-core-70-Apply-Template-for-Base-IGs/ValueSet-at-funktionscode-vs.xlsx
+++ b/r5-core-70-Apply-Template-for-Base-IGs/ValueSet-at-funktionscode-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T16:16:44+00:00</t>
+    <t>2026-10-16T17:20:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-70-Apply-Template-for-Base-IGs/ValueSet-at-funktionscode-vs.xlsx
+++ b/r5-core-70-Apply-Template-for-Base-IGs/ValueSet-at-funktionscode-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T17:20:45+00:00</t>
+    <t>2026-10-17T09:55:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
